--- a/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M08/first/CF_M08_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M08/first/CF_M08_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9677</v>
       </c>
       <c r="D13" t="n">
+        <v>0.9677</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9779</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system must have an affiliation/plans system for companies that want to have certain advantages (it has three plans: free, basic, and premium).</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Constraint</t>
@@ -772,10 +776,6 @@
           <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,14 +806,11 @@
           <t>Compatibility tests demonstrating functionality across major browsers and mobile devices.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>R_26</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -827,14 +824,11 @@
           <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>CF_M08_R25</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -865,10 +859,6 @@
           <t>Every product must have a default route in which the user returns it on their own and with their own means.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -882,10 +872,6 @@
           <t>Every product must have a predetermined route in which the user returns it on his own account and with his own means.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -916,14 +902,11 @@
           <t>The system will be in both Spanish and English (verified by a translator).</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>R_16</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -937,14 +920,11 @@
           <t>The system should support Spanish and English (verified by a translator).</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CF_M08_R15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -975,14 +955,11 @@
           <t>Verify that only company users can access their products/routes/profile.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -996,14 +973,11 @@
           <t>Verify that only Business Users can access their products/routes/profile.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M08_R29</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1039,9 +1013,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1065,8 +1036,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1097,10 +1066,6 @@
           <t>Un usuario can be both a donor and a company.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1114,10 +1079,6 @@
           <t>A user can be both a donor and a company.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1153,9 +1114,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1174,9 +1132,6 @@
           <t>CF_M08_C04</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1207,14 +1162,11 @@
           <t>Complete and updated documentation, and average time for implementing updates and problem resolution not exceeding 2 hours.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_24</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1228,14 +1180,11 @@
           <t>Complete and up-to-date documentation, and average implementation time for updates and problem resolution not exceeding 2 hours.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M08_R23</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1266,10 +1215,6 @@
           <t>A company must be able to modify its profile/public page at all times, as well as preview it while editing.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1283,10 +1228,6 @@
           <t>A company must be able to modify its public profile/page at any time and preview it while editing</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1317,14 +1258,11 @@
           <t>The system must pass security audits without critical vulnerabilities.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1338,14 +1276,11 @@
           <t xml:space="preserve"> The system must pass security audits data without critical vulnerabilities.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CF_M08_R19</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1376,14 +1311,11 @@
           <t>Conducting usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1397,14 +1329,11 @@
           <t>Performance of usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M08_R17</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1440,9 +1369,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1461,9 +1387,6 @@
           <t>CF_M08_C05</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1494,10 +1417,6 @@
           <t>The system must be able to save all images of all products/users in the system.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1511,10 +1430,6 @@
           <t>The system must be able to save all the images of all the products and users of the system.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1545,10 +1460,6 @@
           <t>The system must allow registering new users to the system.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1562,10 +1473,6 @@
           <t>The system must allow new users to register in the system.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1596,14 +1503,11 @@
           <t>Ability to increase server resources and maintain performance with a 50% increase in workload.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_28</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1617,14 +1521,11 @@
           <t>Capacity to increase the resources of the server and maintain performance with a 50% increase in workload.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M08_R27</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1655,10 +1556,6 @@
           <t>The system must allow logged-in or non-logged-in users to view the profiles of the different companies as well as their products.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1672,10 +1569,6 @@
           <t>The system must allow users logged-in or non-logged-in to see the profiles and products of the different companies.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1706,10 +1599,6 @@
           <t>Every route must have an associated budget (which can be 0) which the user must be able to pay through the use of the system when returning the product.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1723,10 +1612,6 @@
           <t>Every route must have an associated budget (can be 0) which the user must be able to pay using the system when returning the product.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1757,10 +1642,6 @@
           <t>A company must be able to register a product and make it visible on its profile/public page.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1774,10 +1655,6 @@
           <t>A company must be able to register a product and have it visible on its profile/page public.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1813,9 +1690,6 @@
           <t>C_08</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1839,8 +1713,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1871,14 +1743,11 @@
           <t>Uptime monitoring that demonstrates 99.9% uptime and disaster recovery tests that meet the specified recovery time.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_22</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1892,14 +1761,11 @@
           <t>Uptime monitoring demonstrating 99.9% uptime and disaster recovery testing that meets the specified recovery time.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M08_R21</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1935,9 +1801,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1961,8 +1824,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1993,10 +1854,6 @@
           <t>A company must have access to the system dashboard in order to use the various internal functionalities and additional information (statistics, values, etc.).</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2010,10 +1867,6 @@
           <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2044,10 +1897,6 @@
           <t>A user must be able to return a product registered by a company through the use of its routes.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2061,10 +1910,6 @@
           <t>A user must be able to return a product registered in a company throug the use of its routes.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2100,9 +1945,6 @@
           <t>C_07</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2126,8 +1968,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2158,10 +1998,6 @@
           <t>The system must allow users to log out.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2175,10 +2011,6 @@
           <t>The system must allow users to log out.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2214,9 +2046,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2240,8 +2069,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2277,9 +2104,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2303,8 +2127,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2335,10 +2157,6 @@
           <t>The system must be able to authenticate existing users through email.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2352,10 +2170,6 @@
           <t>The system must be able to authenticate existing users through email.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2386,10 +2200,6 @@
           <t>A company must be able to register a route to link it to its products.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2403,10 +2213,6 @@
           <t>A company must be able to register a route to link it to its products.</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
